--- a/05_Figures/F06_prediction/proteins/T3/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_fcsa_I/spls/c_data/results.xlsx
@@ -923,7 +923,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.140441716608581</v>
@@ -931,10 +931,18 @@
       <c r="I3" t="n">
         <v>0.375</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.139303482587065</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0945273631840796</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.741729788384832</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.683380586206716</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -958,6 +966,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.88349796728892</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.738125739309205</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0806850413486172</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.955934311297221</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.223593478035959</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.50957378154263</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.422577771916363</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.480451696184569</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.09918414628132</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.56214042467862</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.382239629129701</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.261651616082873</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.04665021523641</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.704502668823882</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.20901650644343</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2.08341929893369</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.399858613467907</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.685570565919986</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.151074427418176</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.718702943830638</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.26903983060925</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.66904733465575</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.321756297056909</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-3.12088712966782</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.509262679623924</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.444643703263636</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.694272784143908</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-1.21831045373113</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.19789261248541</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.457249462087247</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.20232538576006</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.358901236394307</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.82231884425285</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.30526934631847</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.143788268565709</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.195210071252472</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.673732434973896</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.528770303851908</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.17800889499601</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.56106952507606</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.20260638461301</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.322729901309272</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.0684468081324265</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.458248862239102</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.16867445528395</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.182605576457</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-2.72200469299655</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.00761380734669515</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.249714898662662</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.869077321998672</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.871267272769231</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.388412190910903</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0588797320613936</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.640309711563222</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.71618778379082</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.6054835874699</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.9000685556937</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.447556913430888</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.832378302345164</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.246642501585318</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.641992068091997</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.681524207669087</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.978234022450708</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.440862315756387</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.167727514005502</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.175866421616382</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.609944513500019</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.649102467112359</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.0914962659925544</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.570958771245134</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.406710560445756</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.585387124263553</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.640389732943469</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.219486567104381</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.10288079396853</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.348748563392012</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.23201258853071</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-2.7739433281142</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.08256107755992</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.880825843264063</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.04684712013269</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-1.1688919289032</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.3239586515694</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.815457115836101</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.178769318098795</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.352249653940652</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.14598479265474</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.87522012360977</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.433469114910286</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.265024987823449</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.346206755504576</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.0658744570606045</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.550680976635649</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.545130867945539</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.795759009644637</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.599263939883284</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.764694000803747</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.417760826873624</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.37616518009033</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.421630638459287</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-3.27537608368918</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.551936054779036</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.66627292683949</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.50840201227058</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.485486296954927</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.787866136676016</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.2249618681951</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.796747612346676</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.910138186453278</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.19792485300765</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-2.50869863225973</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.562370866218374</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.00440175623376027</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.52796998662033</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.27402769797227</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.38623615898669</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.872460770707778</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.00074772675808</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.48657022220083</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.269568999982216</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.559809642168702</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.190359314696522</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.383868725787183</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.275940137203887</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.306758350832318</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.23502781658234</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.822955141563465</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.695903988819796</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.388502039582178</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.193040222837749</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.765605241324392</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.839509451230035</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.37303879552874</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-2.16620033444018</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.725763812882594</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.44307017859659</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.838861757011053</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.941912533494553</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.0457545080109782</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.706933413311541</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.54248797533761</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.26649377413746</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.532789774977062</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.896647837313516</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.919902707075848</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.5124698035961</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.326171393358486</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.775853600303498</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.457625313550729</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.0241100404567169</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-2.94354896517941</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.486124212191028</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.705728761591753</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.468886533700076</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.76074651887476</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.262942315138012</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.03804086574799</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.672466158463809</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.28238982282654</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.527558460024264</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.6717719977109</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-1.09896574896022</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.269455237421691</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.335227639310026</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.0331488230033088</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.52089799567521</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.464767319879942</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.179174596052074</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.178206181304657</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.410381187937113</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.609608275059509</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.362729536555202</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.103266218898975</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.152339526802352</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.524989646753047</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.64134762873796</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.59930532090654</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.40960445552439</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.321689248843718</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.282059752824593</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.01121795877942</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.140145535394279</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.30293066435023</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.162388262174254</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.299835711961801</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.197074988502557</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.48526469200624</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.533935137719688</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.47225800289429</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.72533795860012</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.39359821658272</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.533693214394802</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.765225919382919</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-1.83254281904617</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.777080107076984</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.06390374244292</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.460906267257786</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.03776909645786</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.0901135239529969</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.590601368357729</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
